--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XI-XX/FRACC XVIII/LTAIPT_A63F18.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XI-XX/FRACC XVIII/LTAIPT_A63F18.xlsx
@@ -9,16 +9,18 @@
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
     <sheet name="Hidden_1" sheetId="2" r:id="rId2"/>
+    <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="Hidden_113">Hidden_1!$A$1:$A$2</definedName>
+    <definedName name="Hidden_17">Hidden_1!$A$1:$A$2</definedName>
+    <definedName name="Hidden_214">Hidden_2!$A$1:$A$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="94">
   <si>
     <t>48967</t>
   </si>
@@ -44,12 +46,12 @@
     <t>4</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -80,6 +82,9 @@
     <t>436088</t>
   </si>
   <si>
+    <t>571929</t>
+  </si>
+  <si>
     <t>436071</t>
   </si>
   <si>
@@ -176,10 +181,13 @@
     <t xml:space="preserve">Segundo apellido del (la) servidor(a) público(a) </t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
     <t>Clave o nivel del puesto</t>
   </si>
   <si>
-    <t>Denominación del puesto</t>
+    <t>Denominación del puesto (de acuerdo con el catálogo que en su caso regule la actividad del sujeto obligado) (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t>Denominación del cargo</t>
@@ -251,34 +259,43 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>203EA98053BE9F70ABFC5079999FBE19</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>5FCF41236C5D6CCA487FA96C8C03BC8E</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
   </si>
   <si>
     <t>Ver nota</t>
   </si>
   <si>
+    <t>Este dato no se requiere para este periodo, de conformidad con las últimas modificaciones a los Lineamientos Técnicos Generales, aprobadas por el Pleno del Consejo Nacional del Sistema Nacional de Transparencia.</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
     <t>Contraloría Interna</t>
   </si>
   <si>
-    <t>16/01/2023</t>
+    <t>24/04/2023</t>
   </si>
   <si>
     <t>29/04/2021</t>
   </si>
   <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022 la Contraloría  Interna del Colegio de Bachilleres del Estado de Tlaxcala  no ha emitido alguna sanción administrativa a servidores públicos de esta Dependencia o Entidad Pública.</t>
+    <t>Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023 la Contraloría  Interna del Colegio de Bachilleres del Estado de Tlaxcala  no ha emitido alguna sanción administrativa a servidores públicos de esta Dependencia o Entidad Pública.</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
   <si>
     <t>Federal</t>
@@ -677,49 +694,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AG8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="35.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="40.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="56.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="38.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="43.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="32" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="53.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="58.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="48.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="41.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="43.28515625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="43.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="20" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="213.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="126.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="56.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="32" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="53.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="58.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="48.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="41.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="20" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="208.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -736,7 +754,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -751,7 +769,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -771,7 +789,7 @@
         <v>6</v>
       </c>
       <c r="H4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I4" t="s">
         <v>6</v>
@@ -783,70 +801,73 @@
         <v>6</v>
       </c>
       <c r="L4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O4" t="s">
         <v>8</v>
-      </c>
-      <c r="M4" t="s">
-        <v>6</v>
-      </c>
-      <c r="N4" t="s">
-        <v>9</v>
-      </c>
-      <c r="O4" t="s">
-        <v>6</v>
       </c>
       <c r="P4" t="s">
         <v>6</v>
       </c>
       <c r="Q4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R4" t="s">
         <v>7</v>
       </c>
-      <c r="R4" t="s">
-        <v>8</v>
-      </c>
       <c r="S4" t="s">
+        <v>9</v>
+      </c>
+      <c r="T4" t="s">
         <v>6</v>
       </c>
-      <c r="T4" t="s">
-        <v>8</v>
-      </c>
       <c r="U4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W4" t="s">
         <v>7</v>
       </c>
       <c r="X4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y4" t="s">
         <v>10</v>
       </c>
       <c r="Z4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA4" t="s">
         <v>11</v>
       </c>
       <c r="AB4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC4" t="s">
         <v>7</v>
       </c>
-      <c r="AC4" t="s">
-        <v>8</v>
-      </c>
       <c r="AD4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE4" t="s">
         <v>7</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>12</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
@@ -940,10 +961,13 @@
       <c r="AF5" t="s">
         <v>44</v>
       </c>
+      <c r="AG5" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -976,203 +1000,210 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
+      <c r="AG6" s="4"/>
     </row>
-    <row r="7" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
+      </c>
+      <c r="AG8" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="A6:AG6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1180,9 +1211,12 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N8:N198">
-      <formula1>Hidden_113</formula1>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H8:H201">
+      <formula1>Hidden_17</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O8:O201">
+      <formula1>Hidden_214</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1196,12 +1230,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
